--- a/rules/CORE-000137/negative/01/data/unit-test-coreid-CG0100-negative 1.xlsx
+++ b/rules/CORE-000137/negative/01/data/unit-test-coreid-CG0100-negative 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\core-contributor\rules\CORE-000137\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C1F06E-087F-4B87-A398-8CA1FBE5271F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B771E55-65F3-4256-B58E-B2B7E998F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="99">
   <si>
     <t>Product</t>
   </si>
@@ -392,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -415,13 +415,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -778,7 +771,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1020,6 +1013,77 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1339,14 +1403,12 @@
       <c r="G5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="12">
+      <c r="H5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="6">
         <v>8</v>
       </c>
-      <c r="K5" s="11"/>
       <c r="L5" s="5" t="s">
         <v>68</v>
       </c>
@@ -1406,14 +1468,12 @@
       <c r="G6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="12">
+      <c r="H6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="6">
         <v>1</v>
       </c>
-      <c r="K6" s="11"/>
       <c r="L6" s="5" t="s">
         <v>68</v>
       </c>
@@ -1473,14 +1533,12 @@
       <c r="G7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="12">
+      <c r="H7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="6">
         <v>2</v>
       </c>
-      <c r="K7" s="11"/>
       <c r="L7" s="5" t="s">
         <v>68</v>
       </c>
@@ -1540,14 +1598,12 @@
       <c r="G8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="12">
+      <c r="H8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="6">
         <v>2</v>
       </c>
-      <c r="K8" s="11"/>
       <c r="L8" s="5" t="s">
         <v>68</v>
       </c>
@@ -1607,14 +1663,12 @@
       <c r="G9" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="10">
+      <c r="H9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="5">
         <v>5</v>
       </c>
-      <c r="K9" s="11"/>
       <c r="L9" s="5" t="s">
         <v>68</v>
       </c>
@@ -1741,14 +1795,12 @@
       <c r="G11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="10">
+      <c r="H11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="5">
         <v>5</v>
       </c>
-      <c r="K11" s="11"/>
       <c r="L11" s="5" t="s">
         <v>68</v>
       </c>
@@ -1808,14 +1860,12 @@
       <c r="G12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="12">
+      <c r="H12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="6">
         <v>1</v>
       </c>
-      <c r="K12" s="11"/>
       <c r="L12" s="5" t="s">
         <v>68</v>
       </c>
@@ -1875,14 +1925,12 @@
       <c r="G13" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="12">
+      <c r="H13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="6">
         <v>3</v>
       </c>
-      <c r="K13" s="11"/>
       <c r="L13" s="5" t="s">
         <v>68</v>
       </c>
@@ -1942,14 +1990,12 @@
       <c r="G14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="12">
+      <c r="H14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="6">
         <v>4</v>
       </c>
-      <c r="K14" s="11"/>
       <c r="L14" s="5" t="s">
         <v>68</v>
       </c>
@@ -2009,14 +2055,12 @@
       <c r="G15" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="10">
+      <c r="H15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="5">
         <v>5</v>
       </c>
-      <c r="K15" s="11"/>
       <c r="L15" s="5" t="s">
         <v>68</v>
       </c>
@@ -2076,14 +2120,12 @@
       <c r="G16" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="12">
+      <c r="H16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="6">
         <v>100</v>
       </c>
-      <c r="K16" s="11"/>
       <c r="L16" s="5" t="s">
         <v>68</v>
       </c>
@@ -2210,14 +2252,12 @@
       <c r="G18" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="12">
+      <c r="H18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="6">
         <v>1</v>
       </c>
-      <c r="K18" s="11"/>
       <c r="L18" s="5" t="s">
         <v>68</v>
       </c>
@@ -2344,9 +2384,12 @@
       <c r="G20" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="J20" s="6">
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="9">
         <v>-5</v>
       </c>
+      <c r="K20" s="8"/>
       <c r="L20" s="5" t="s">
         <v>68</v>
       </c>
@@ -2406,14 +2449,12 @@
       <c r="G21" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="11"/>
+      <c r="H21" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="J21" s="5">
         <v>5</v>
       </c>
-      <c r="K21" s="11"/>
       <c r="L21" s="5" t="s">
         <v>68</v>
       </c>
